--- a/jpcore-r4/develop/StructureDefinition-JP-Binary.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-JP-Binary.xlsx
@@ -375,7 +375,7 @@
     <t>Binary.meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">バージョン固有の識別子 </t>
+    <t>バージョン固有の識別子</t>
   </si>
   <si>
     <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
